--- a/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
+++ b/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="78">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
   <si>
     <t>Record</t>
   </si>
@@ -33,223 +33,217 @@
     <t>Dave's Dynamos</t>
   </si>
   <si>
+    <t>Jeffrey's Team THAT NEVER WINS</t>
+  </si>
+  <si>
+    <t>Tracey Time</t>
+  </si>
+  <si>
+    <t>Yahya's Crew</t>
+  </si>
+  <si>
+    <t>MARVIN's Magnificent Team</t>
+  </si>
+  <si>
+    <t>Sporty Jess</t>
+  </si>
+  <si>
     <t>Graesser's Golden Receivers</t>
   </si>
   <si>
-    <t>Sporty Jess</t>
-  </si>
-  <si>
-    <t>Tracey Time</t>
-  </si>
-  <si>
-    <t>Jeffrey's Team THAT NEVER WINS</t>
-  </si>
-  <si>
     <t>Team Schottler</t>
   </si>
   <si>
-    <t>Yahya's Crew</t>
-  </si>
-  <si>
-    <t>MARVIN's Magnificent Team</t>
-  </si>
-  <si>
     <t>Hannah's Hail Mary</t>
   </si>
   <si>
+    <t>Laces Out Dan</t>
+  </si>
+  <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
   <si>
+    <t>Yangblood Bravesheart</t>
+  </si>
+  <si>
     <t>Ishan's Impressive Team</t>
   </si>
   <si>
     <t>Dale's Dangerous Team</t>
   </si>
   <si>
-    <t>Yangblood Bravesheart</t>
-  </si>
-  <si>
-    <t>Laces Out Dan</t>
-  </si>
-  <si>
-    <t>2-0</t>
-  </si>
-  <si>
-    <t>1-1</t>
-  </si>
-  <si>
-    <t>0-2</t>
-  </si>
-  <si>
-    <t>99.5%</t>
-  </si>
-  <si>
-    <t>98.1%</t>
-  </si>
-  <si>
-    <t>86.3%</t>
-  </si>
-  <si>
-    <t>84.6%</t>
-  </si>
-  <si>
-    <t>83.2%</t>
-  </si>
-  <si>
-    <t>55.1%</t>
-  </si>
-  <si>
-    <t>40.2%</t>
-  </si>
-  <si>
-    <t>26.3%</t>
-  </si>
-  <si>
-    <t>13.4%</t>
-  </si>
-  <si>
-    <t>6.4%</t>
-  </si>
-  <si>
-    <t>5.0%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>-19900</t>
-  </si>
-  <si>
-    <t>-5163</t>
-  </si>
-  <si>
-    <t>-630</t>
-  </si>
-  <si>
-    <t>-549</t>
-  </si>
-  <si>
-    <t>-495</t>
-  </si>
-  <si>
-    <t>-123</t>
-  </si>
-  <si>
-    <t>+149</t>
-  </si>
-  <si>
-    <t>+280</t>
-  </si>
-  <si>
-    <t>+646</t>
-  </si>
-  <si>
-    <t>+1462</t>
-  </si>
-  <si>
-    <t>+1900</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+19900</t>
+    <t>3-0</t>
+  </si>
+  <si>
+    <t>2-1</t>
+  </si>
+  <si>
+    <t>1-2</t>
+  </si>
+  <si>
+    <t>0-3</t>
+  </si>
+  <si>
+    <t>97.0%</t>
+  </si>
+  <si>
+    <t>91.4%</t>
+  </si>
+  <si>
+    <t>81.4%</t>
+  </si>
+  <si>
+    <t>77.2%</t>
+  </si>
+  <si>
+    <t>75.0%</t>
+  </si>
+  <si>
+    <t>64.0%</t>
+  </si>
+  <si>
+    <t>60.9%</t>
+  </si>
+  <si>
+    <t>50.2%</t>
+  </si>
+  <si>
+    <t>1.3%</t>
+  </si>
+  <si>
+    <t>1.0%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.2%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-3233</t>
+  </si>
+  <si>
+    <t>-1063</t>
+  </si>
+  <si>
+    <t>-438</t>
+  </si>
+  <si>
+    <t>-339</t>
+  </si>
+  <si>
+    <t>-300</t>
+  </si>
+  <si>
+    <t>-178</t>
+  </si>
+  <si>
+    <t>-156</t>
+  </si>
+  <si>
+    <t>-101</t>
+  </si>
+  <si>
+    <t>+7592</t>
+  </si>
+  <si>
+    <t>+9900</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>+49900</t>
+  </si>
+  <si>
+    <t>+99900</t>
   </si>
   <si>
     <t>Probability</t>
   </si>
   <si>
-    <t>52.8%</t>
-  </si>
-  <si>
-    <t>22.8%</t>
-  </si>
-  <si>
-    <t>13.2%</t>
-  </si>
-  <si>
-    <t>7.4%</t>
-  </si>
-  <si>
-    <t>2.3%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-112</t>
-  </si>
-  <si>
-    <t>+339</t>
-  </si>
-  <si>
-    <t>+658</t>
-  </si>
-  <si>
-    <t>+1251</t>
-  </si>
-  <si>
-    <t>+4248</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>+49900</t>
-  </si>
-  <si>
-    <t>+∞</t>
-  </si>
-  <si>
-    <t>38.9%</t>
-  </si>
-  <si>
-    <t>23.8%</t>
-  </si>
-  <si>
-    <t>17.6%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>5.9%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>+157</t>
-  </si>
-  <si>
-    <t>+320</t>
-  </si>
-  <si>
-    <t>+468</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+1595</t>
-  </si>
-  <si>
-    <t>+2678</t>
+    <t>42.7%</t>
+  </si>
+  <si>
+    <t>20.3%</t>
+  </si>
+  <si>
+    <t>12.4%</t>
+  </si>
+  <si>
+    <t>8.5%</t>
+  </si>
+  <si>
+    <t>7.5%</t>
+  </si>
+  <si>
+    <t>3.8%</t>
+  </si>
+  <si>
+    <t>3.1%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>+134</t>
+  </si>
+  <si>
+    <t>+393</t>
+  </si>
+  <si>
+    <t>+706</t>
+  </si>
+  <si>
+    <t>+1076</t>
+  </si>
+  <si>
+    <t>+1233</t>
+  </si>
+  <si>
+    <t>+2532</t>
+  </si>
+  <si>
+    <t>+3126</t>
+  </si>
+  <si>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>62.6%</t>
+  </si>
+  <si>
+    <t>17.7%</t>
+  </si>
+  <si>
+    <t>6.5%</t>
+  </si>
+  <si>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>3.3%</t>
+  </si>
+  <si>
+    <t>-167</t>
+  </si>
+  <si>
+    <t>+465</t>
+  </si>
+  <si>
+    <t>+1438</t>
+  </si>
+  <si>
+    <t>+2841</t>
+  </si>
+  <si>
+    <t>+2930</t>
   </si>
 </sst>
 </file>
@@ -632,10 +626,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -643,13 +637,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -660,10 +654,10 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -671,13 +665,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -685,13 +679,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -702,10 +696,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -716,10 +710,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -727,13 +721,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -741,13 +735,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -758,10 +752,10 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -769,13 +763,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -786,10 +780,10 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -800,10 +794,10 @@
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -811,13 +805,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -838,7 +832,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -852,10 +846,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="D2" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -863,13 +857,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -880,122 +874,122 @@
         <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="D4" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B5" t="s">
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="D5" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="D6" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="D7" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="D8" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D9" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1006,38 +1000,38 @@
         <v>20</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>
@@ -1058,7 +1052,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1069,13 +1063,13 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
         <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1089,161 +1083,161 @@
         <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
         <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C6" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>54</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>63</v>
+        <v>48</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B13" t="s">
         <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="B14" t="s">
         <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1254,10 +1248,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>56</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>65</v>
+        <v>48</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
+++ b/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="76">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="77">
   <si>
     <t>Record</t>
   </si>
@@ -30,91 +30,94 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Tracey Time</t>
+  </si>
+  <si>
+    <t>Yahya's Crew</t>
+  </si>
+  <si>
+    <t>Team Schottler</t>
+  </si>
+  <si>
+    <t>Graesser's Golden Receivers</t>
+  </si>
+  <si>
+    <t>Jeffrey's Team THAT NEVER WINS</t>
+  </si>
+  <si>
+    <t>MARVIN's Magnificent Team</t>
+  </si>
+  <si>
     <t>Dave's Dynamos</t>
   </si>
   <si>
-    <t>Jeffrey's Team THAT NEVER WINS</t>
-  </si>
-  <si>
-    <t>Tracey Time</t>
-  </si>
-  <si>
-    <t>Yahya's Crew</t>
-  </si>
-  <si>
-    <t>MARVIN's Magnificent Team</t>
-  </si>
-  <si>
     <t>Sporty Jess</t>
   </si>
   <si>
-    <t>Graesser's Golden Receivers</t>
-  </si>
-  <si>
-    <t>Team Schottler</t>
-  </si>
-  <si>
     <t>Hannah's Hail Mary</t>
   </si>
   <si>
+    <t>Dale's Dangerous Team</t>
+  </si>
+  <si>
+    <t>Yangblood Bravesheart</t>
+  </si>
+  <si>
     <t>Laces Out Dan</t>
   </si>
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
   <si>
-    <t>Yangblood Bravesheart</t>
-  </si>
-  <si>
     <t>Ishan's Impressive Team</t>
   </si>
   <si>
-    <t>Dale's Dangerous Team</t>
-  </si>
-  <si>
-    <t>3-0</t>
-  </si>
-  <si>
-    <t>2-1</t>
-  </si>
-  <si>
-    <t>1-2</t>
-  </si>
-  <si>
-    <t>0-3</t>
-  </si>
-  <si>
-    <t>97.0%</t>
-  </si>
-  <si>
-    <t>91.4%</t>
-  </si>
-  <si>
-    <t>81.4%</t>
-  </si>
-  <si>
-    <t>77.2%</t>
-  </si>
-  <si>
-    <t>75.0%</t>
-  </si>
-  <si>
-    <t>64.0%</t>
-  </si>
-  <si>
-    <t>60.9%</t>
-  </si>
-  <si>
-    <t>50.2%</t>
-  </si>
-  <si>
-    <t>1.3%</t>
-  </si>
-  <si>
-    <t>1.0%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
+    <t>4-0</t>
+  </si>
+  <si>
+    <t>3-1</t>
+  </si>
+  <si>
+    <t>2-2</t>
+  </si>
+  <si>
+    <t>1-3</t>
+  </si>
+  <si>
+    <t>0-4</t>
+  </si>
+  <si>
+    <t>95.0%</t>
+  </si>
+  <si>
+    <t>93.7%</t>
+  </si>
+  <si>
+    <t>91.8%</t>
+  </si>
+  <si>
+    <t>83.5%</t>
+  </si>
+  <si>
+    <t>68.9%</t>
+  </si>
+  <si>
+    <t>62.9%</t>
+  </si>
+  <si>
+    <t>61.7%</t>
+  </si>
+  <si>
+    <t>34.7%</t>
+  </si>
+  <si>
+    <t>6.2%</t>
+  </si>
+  <si>
+    <t>0.7%</t>
+  </si>
+  <si>
+    <t>0.6%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -126,37 +129,37 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-3233</t>
-  </si>
-  <si>
-    <t>-1063</t>
-  </si>
-  <si>
-    <t>-438</t>
-  </si>
-  <si>
-    <t>-339</t>
-  </si>
-  <si>
-    <t>-300</t>
-  </si>
-  <si>
-    <t>-178</t>
-  </si>
-  <si>
-    <t>-156</t>
-  </si>
-  <si>
-    <t>-101</t>
-  </si>
-  <si>
-    <t>+7592</t>
-  </si>
-  <si>
-    <t>+9900</t>
-  </si>
-  <si>
-    <t>+33233</t>
+    <t>-1900</t>
+  </si>
+  <si>
+    <t>-1487</t>
+  </si>
+  <si>
+    <t>-1120</t>
+  </si>
+  <si>
+    <t>-506</t>
+  </si>
+  <si>
+    <t>-222</t>
+  </si>
+  <si>
+    <t>-170</t>
+  </si>
+  <si>
+    <t>-161</t>
+  </si>
+  <si>
+    <t>+188</t>
+  </si>
+  <si>
+    <t>+1513</t>
+  </si>
+  <si>
+    <t>+14186</t>
+  </si>
+  <si>
+    <t>+16567</t>
   </si>
   <si>
     <t>+49900</t>
@@ -168,82 +171,82 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>42.7%</t>
-  </si>
-  <si>
-    <t>20.3%</t>
-  </si>
-  <si>
-    <t>12.4%</t>
-  </si>
-  <si>
-    <t>8.5%</t>
-  </si>
-  <si>
-    <t>7.5%</t>
-  </si>
-  <si>
-    <t>3.8%</t>
+    <t>31.8%</t>
+  </si>
+  <si>
+    <t>25.5%</t>
+  </si>
+  <si>
+    <t>21.4%</t>
+  </si>
+  <si>
+    <t>11.1%</t>
+  </si>
+  <si>
+    <t>3.6%</t>
   </si>
   <si>
     <t>3.1%</t>
   </si>
   <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>+134</t>
-  </si>
-  <si>
-    <t>+393</t>
-  </si>
-  <si>
-    <t>+706</t>
-  </si>
-  <si>
-    <t>+1076</t>
-  </si>
-  <si>
-    <t>+1233</t>
-  </si>
-  <si>
-    <t>+2532</t>
+    <t>2.8%</t>
+  </si>
+  <si>
+    <t>+214</t>
+  </si>
+  <si>
+    <t>+292</t>
+  </si>
+  <si>
+    <t>+367</t>
+  </si>
+  <si>
+    <t>+801</t>
+  </si>
+  <si>
+    <t>+2678</t>
   </si>
   <si>
     <t>+3126</t>
   </si>
   <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>62.6%</t>
-  </si>
-  <si>
-    <t>17.7%</t>
-  </si>
-  <si>
-    <t>6.5%</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>3.3%</t>
-  </si>
-  <si>
-    <t>-167</t>
-  </si>
-  <si>
-    <t>+465</t>
-  </si>
-  <si>
-    <t>+1438</t>
-  </si>
-  <si>
-    <t>+2841</t>
-  </si>
-  <si>
-    <t>+2930</t>
+    <t>+3471</t>
+  </si>
+  <si>
+    <t>55.6%</t>
+  </si>
+  <si>
+    <t>27.3%</t>
+  </si>
+  <si>
+    <t>9.7%</t>
+  </si>
+  <si>
+    <t>4.8%</t>
+  </si>
+  <si>
+    <t>2.1%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>-125</t>
+  </si>
+  <si>
+    <t>+266</t>
+  </si>
+  <si>
+    <t>+931</t>
+  </si>
+  <si>
+    <t>+1983</t>
+  </si>
+  <si>
+    <t>+4662</t>
+  </si>
+  <si>
+    <t>+24900</t>
   </si>
 </sst>
 </file>
@@ -626,10 +629,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -640,10 +643,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -651,13 +654,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -668,10 +671,10 @@
         <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -679,13 +682,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -696,10 +699,10 @@
         <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -710,10 +713,10 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -724,10 +727,10 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -738,10 +741,10 @@
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -749,13 +752,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -763,13 +766,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -777,13 +780,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -791,13 +794,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -808,10 +811,10 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -832,7 +835,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -840,13 +843,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D2" t="s">
         <v>58</v>
@@ -854,13 +857,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D3" t="s">
         <v>59</v>
@@ -871,10 +874,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C4" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D4" t="s">
         <v>60</v>
@@ -882,13 +885,13 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D5" t="s">
         <v>61</v>
@@ -896,13 +899,13 @@
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D6" t="s">
         <v>62</v>
@@ -910,13 +913,13 @@
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D7" t="s">
         <v>63</v>
@@ -930,7 +933,7 @@
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="D8" t="s">
         <v>64</v>
@@ -944,15 +947,15 @@
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
@@ -961,77 +964,77 @@
         <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="B14" t="s">
         <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="B15" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>
@@ -1052,7 +1055,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1066,7 +1069,7 @@
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D2" t="s">
         <v>71</v>
@@ -1077,10 +1080,10 @@
         <v>16</v>
       </c>
       <c r="B3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D3" t="s">
         <v>72</v>
@@ -1088,13 +1091,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D4" t="s">
         <v>73</v>
@@ -1102,156 +1105,156 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
         <v>68</v>
       </c>
       <c r="D5" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
         <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C7" t="s">
         <v>70</v>
       </c>
       <c r="D7" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D9" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="B10" t="s">
         <v>18</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D10" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B11" t="s">
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D12" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D14" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B15" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="D15" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
+++ b/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="77">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="71">
   <si>
     <t>Record</t>
   </si>
@@ -30,94 +30,91 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Yahya's Crew</t>
+  </si>
+  <si>
+    <t>Graesser's Golden Receivers</t>
+  </si>
+  <si>
+    <t>MARVIN's Magnificent Team</t>
+  </si>
+  <si>
     <t>Tracey Time</t>
   </si>
   <si>
-    <t>Yahya's Crew</t>
+    <t>Dave's Dynamos</t>
   </si>
   <si>
     <t>Team Schottler</t>
   </si>
   <si>
-    <t>Graesser's Golden Receivers</t>
+    <t>Sporty Jess</t>
+  </si>
+  <si>
+    <t>Hannah's Hail Mary</t>
   </si>
   <si>
     <t>Jeffrey's Team THAT NEVER WINS</t>
   </si>
   <si>
-    <t>MARVIN's Magnificent Team</t>
-  </si>
-  <si>
-    <t>Dave's Dynamos</t>
-  </si>
-  <si>
-    <t>Sporty Jess</t>
-  </si>
-  <si>
-    <t>Hannah's Hail Mary</t>
-  </si>
-  <si>
     <t>Dale's Dangerous Team</t>
   </si>
   <si>
     <t>Yangblood Bravesheart</t>
   </si>
   <si>
+    <t>Bears, Jags, Foxes, Oh My!</t>
+  </si>
+  <si>
     <t>Laces Out Dan</t>
   </si>
   <si>
-    <t>Bears, Jags, Foxes, Oh My!</t>
-  </si>
-  <si>
     <t>Ishan's Impressive Team</t>
   </si>
   <si>
-    <t>4-0</t>
-  </si>
-  <si>
-    <t>3-1</t>
-  </si>
-  <si>
-    <t>2-2</t>
-  </si>
-  <si>
-    <t>1-3</t>
-  </si>
-  <si>
-    <t>0-4</t>
-  </si>
-  <si>
-    <t>95.0%</t>
-  </si>
-  <si>
-    <t>93.7%</t>
-  </si>
-  <si>
-    <t>91.8%</t>
-  </si>
-  <si>
-    <t>83.5%</t>
-  </si>
-  <si>
-    <t>68.9%</t>
-  </si>
-  <si>
-    <t>62.9%</t>
-  </si>
-  <si>
-    <t>61.7%</t>
-  </si>
-  <si>
-    <t>34.7%</t>
-  </si>
-  <si>
-    <t>6.2%</t>
-  </si>
-  <si>
-    <t>0.7%</t>
-  </si>
-  <si>
-    <t>0.6%</t>
+    <t>4-1</t>
+  </si>
+  <si>
+    <t>2-3</t>
+  </si>
+  <si>
+    <t>3-2</t>
+  </si>
+  <si>
+    <t>0-5</t>
+  </si>
+  <si>
+    <t>1-4</t>
+  </si>
+  <si>
+    <t>98.9%</t>
+  </si>
+  <si>
+    <t>97.4%</t>
+  </si>
+  <si>
+    <t>82.7%</t>
+  </si>
+  <si>
+    <t>80.5%</t>
+  </si>
+  <si>
+    <t>76.3%</t>
+  </si>
+  <si>
+    <t>69.5%</t>
+  </si>
+  <si>
+    <t>37.1%</t>
+  </si>
+  <si>
+    <t>29.1%</t>
+  </si>
+  <si>
+    <t>23.9%</t>
+  </si>
+  <si>
+    <t>4.2%</t>
   </si>
   <si>
     <t>0.2%</t>
@@ -129,37 +126,34 @@
     <t>0.0%</t>
   </si>
   <si>
-    <t>-1900</t>
-  </si>
-  <si>
-    <t>-1487</t>
-  </si>
-  <si>
-    <t>-1120</t>
-  </si>
-  <si>
-    <t>-506</t>
-  </si>
-  <si>
-    <t>-222</t>
-  </si>
-  <si>
-    <t>-170</t>
-  </si>
-  <si>
-    <t>-161</t>
-  </si>
-  <si>
-    <t>+188</t>
-  </si>
-  <si>
-    <t>+1513</t>
-  </si>
-  <si>
-    <t>+14186</t>
-  </si>
-  <si>
-    <t>+16567</t>
+    <t>-8991</t>
+  </si>
+  <si>
+    <t>-3746</t>
+  </si>
+  <si>
+    <t>-478</t>
+  </si>
+  <si>
+    <t>-413</t>
+  </si>
+  <si>
+    <t>-322</t>
+  </si>
+  <si>
+    <t>-228</t>
+  </si>
+  <si>
+    <t>+170</t>
+  </si>
+  <si>
+    <t>+244</t>
+  </si>
+  <si>
+    <t>+318</t>
+  </si>
+  <si>
+    <t>+2281</t>
   </si>
   <si>
     <t>+49900</t>
@@ -171,82 +165,70 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>31.8%</t>
-  </si>
-  <si>
-    <t>25.5%</t>
-  </si>
-  <si>
-    <t>21.4%</t>
-  </si>
-  <si>
-    <t>11.1%</t>
-  </si>
-  <si>
-    <t>3.6%</t>
-  </si>
-  <si>
-    <t>3.1%</t>
-  </si>
-  <si>
-    <t>2.8%</t>
-  </si>
-  <si>
-    <t>+214</t>
-  </si>
-  <si>
-    <t>+292</t>
-  </si>
-  <si>
-    <t>+367</t>
-  </si>
-  <si>
-    <t>+801</t>
-  </si>
-  <si>
-    <t>+2678</t>
-  </si>
-  <si>
-    <t>+3126</t>
-  </si>
-  <si>
-    <t>+3471</t>
-  </si>
-  <si>
-    <t>55.6%</t>
-  </si>
-  <si>
-    <t>27.3%</t>
-  </si>
-  <si>
-    <t>9.7%</t>
-  </si>
-  <si>
-    <t>4.8%</t>
-  </si>
-  <si>
-    <t>2.1%</t>
-  </si>
-  <si>
-    <t>0.4%</t>
-  </si>
-  <si>
-    <t>-125</t>
-  </si>
-  <si>
-    <t>+266</t>
-  </si>
-  <si>
-    <t>+931</t>
-  </si>
-  <si>
-    <t>+1983</t>
-  </si>
-  <si>
-    <t>+4662</t>
-  </si>
-  <si>
-    <t>+24900</t>
+    <t>52.8%</t>
+  </si>
+  <si>
+    <t>28.9%</t>
+  </si>
+  <si>
+    <t>5.8%</t>
+  </si>
+  <si>
+    <t>5.3%</t>
+  </si>
+  <si>
+    <t>5.1%</t>
+  </si>
+  <si>
+    <t>1.7%</t>
+  </si>
+  <si>
+    <t>-112</t>
+  </si>
+  <si>
+    <t>+246</t>
+  </si>
+  <si>
+    <t>+1624</t>
+  </si>
+  <si>
+    <t>+1787</t>
+  </si>
+  <si>
+    <t>+1861</t>
+  </si>
+  <si>
+    <t>+5782</t>
+  </si>
+  <si>
+    <t>59.4%</t>
+  </si>
+  <si>
+    <t>20.4%</t>
+  </si>
+  <si>
+    <t>16.6%</t>
+  </si>
+  <si>
+    <t>3.2%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>-146</t>
+  </si>
+  <si>
+    <t>+390</t>
+  </si>
+  <si>
+    <t>+502</t>
+  </si>
+  <si>
+    <t>+3025</t>
+  </si>
+  <si>
+    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -632,7 +614,7 @@
         <v>23</v>
       </c>
       <c r="D2" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -640,13 +622,13 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C3" t="s">
         <v>24</v>
       </c>
       <c r="D3" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -654,13 +636,13 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
         <v>25</v>
       </c>
       <c r="D4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -668,13 +650,13 @@
         <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
         <v>26</v>
       </c>
       <c r="D5" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -682,13 +664,13 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
         <v>27</v>
       </c>
       <c r="D6" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -702,7 +684,7 @@
         <v>28</v>
       </c>
       <c r="D7" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -710,13 +692,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
         <v>29</v>
       </c>
       <c r="D8" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -724,13 +706,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
         <v>30</v>
       </c>
       <c r="D9" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -738,13 +720,13 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
         <v>31</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -752,13 +734,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
         <v>32</v>
       </c>
       <c r="D11" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -766,13 +748,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
         <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -786,7 +768,7 @@
         <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -797,10 +779,10 @@
         <v>22</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -808,13 +790,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -835,7 +817,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -843,111 +825,111 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
       </c>
       <c r="C3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C4" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B8" t="s">
         <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
         <v>47</v>
@@ -958,27 +940,27 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -986,13 +968,13 @@
         <v>13</v>
       </c>
       <c r="B12" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -1000,13 +982,13 @@
         <v>17</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1014,27 +996,27 @@
         <v>14</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>
@@ -1055,7 +1037,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1066,97 +1048,97 @@
         <v>17</v>
       </c>
       <c r="B2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C2" t="s">
-        <v>65</v>
+        <v>61</v>
       </c>
       <c r="D2" t="s">
-        <v>71</v>
+        <v>66</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>66</v>
+        <v>62</v>
       </c>
       <c r="D3" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C4" t="s">
-        <v>67</v>
+        <v>63</v>
       </c>
       <c r="D4" t="s">
-        <v>73</v>
+        <v>68</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="D5" t="s">
-        <v>74</v>
+        <v>69</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="D6" t="s">
-        <v>75</v>
+        <v>70</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>70</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>76</v>
+        <v>47</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
       </c>
       <c r="D8" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -1164,97 +1146,97 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D9" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>4</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D10" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D11" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C12" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D12" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="B14" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="D15" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
+++ b/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
   <si>
     <t>Record</t>
   </si>
@@ -30,205 +30,214 @@
     <t>Team</t>
   </si>
   <si>
+    <t>MARVIN's Magnificent Team</t>
+  </si>
+  <si>
     <t>Yahya's Crew</t>
   </si>
   <si>
     <t>Graesser's Golden Receivers</t>
   </si>
   <si>
-    <t>MARVIN's Magnificent Team</t>
+    <t>Dave's Dynamos</t>
   </si>
   <si>
     <t>Tracey Time</t>
   </si>
   <si>
-    <t>Dave's Dynamos</t>
-  </si>
-  <si>
     <t>Team Schottler</t>
   </si>
   <si>
+    <t>Hannah's Hail Mary</t>
+  </si>
+  <si>
     <t>Sporty Jess</t>
   </si>
   <si>
-    <t>Hannah's Hail Mary</t>
+    <t>Dale's Dangerous Team</t>
   </si>
   <si>
     <t>Jeffrey's Team THAT NEVER WINS</t>
   </si>
   <si>
-    <t>Dale's Dangerous Team</t>
-  </si>
-  <si>
     <t>Yangblood Bravesheart</t>
   </si>
   <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
   <si>
+    <t>Ishan's Impressive Team</t>
+  </si>
+  <si>
     <t>Laces Out Dan</t>
   </si>
   <si>
-    <t>Ishan's Impressive Team</t>
-  </si>
-  <si>
-    <t>4-1</t>
-  </si>
-  <si>
-    <t>2-3</t>
-  </si>
-  <si>
-    <t>3-2</t>
-  </si>
-  <si>
-    <t>0-5</t>
-  </si>
-  <si>
-    <t>1-4</t>
-  </si>
-  <si>
-    <t>98.9%</t>
-  </si>
-  <si>
-    <t>97.4%</t>
-  </si>
-  <si>
-    <t>82.7%</t>
-  </si>
-  <si>
-    <t>80.5%</t>
-  </si>
-  <si>
-    <t>76.3%</t>
-  </si>
-  <si>
-    <t>69.5%</t>
-  </si>
-  <si>
-    <t>37.1%</t>
-  </si>
-  <si>
-    <t>29.1%</t>
-  </si>
-  <si>
-    <t>23.9%</t>
+    <t>5-1</t>
+  </si>
+  <si>
+    <t>4-2</t>
+  </si>
+  <si>
+    <t>3-3</t>
+  </si>
+  <si>
+    <t>2-4</t>
+  </si>
+  <si>
+    <t>0-6</t>
+  </si>
+  <si>
+    <t>1-5</t>
+  </si>
+  <si>
+    <t>96.5%</t>
+  </si>
+  <si>
+    <t>95.2%</t>
+  </si>
+  <si>
+    <t>87.1%</t>
+  </si>
+  <si>
+    <t>86.6%</t>
+  </si>
+  <si>
+    <t>85.3%</t>
+  </si>
+  <si>
+    <t>74.3%</t>
+  </si>
+  <si>
+    <t>45.2%</t>
+  </si>
+  <si>
+    <t>12.4%</t>
+  </si>
+  <si>
+    <t>11.0%</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
+    <t>1.4%</t>
+  </si>
+  <si>
+    <t>0.0%</t>
+  </si>
+  <si>
+    <t>-2757</t>
+  </si>
+  <si>
+    <t>-1983</t>
+  </si>
+  <si>
+    <t>-675</t>
+  </si>
+  <si>
+    <t>-646</t>
+  </si>
+  <si>
+    <t>-580</t>
+  </si>
+  <si>
+    <t>-289</t>
+  </si>
+  <si>
+    <t>+121</t>
+  </si>
+  <si>
+    <t>+706</t>
+  </si>
+  <si>
+    <t>+809</t>
+  </si>
+  <si>
+    <t>+1900</t>
+  </si>
+  <si>
+    <t>+7043</t>
+  </si>
+  <si>
+    <t>+99900</t>
+  </si>
+  <si>
+    <t>Probability</t>
+  </si>
+  <si>
+    <t>33.0%</t>
+  </si>
+  <si>
+    <t>28.6%</t>
+  </si>
+  <si>
+    <t>11.8%</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>10.3%</t>
   </si>
   <si>
     <t>4.2%</t>
   </si>
   <si>
+    <t>0.5%</t>
+  </si>
+  <si>
+    <t>0.3%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
+  </si>
+  <si>
+    <t>+203</t>
+  </si>
+  <si>
+    <t>+250</t>
+  </si>
+  <si>
+    <t>+747</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+871</t>
+  </si>
+  <si>
+    <t>+2281</t>
+  </si>
+  <si>
+    <t>+19900</t>
+  </si>
+  <si>
+    <t>+33233</t>
+  </si>
+  <si>
+    <t>60.7%</t>
+  </si>
+  <si>
+    <t>29.5%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
     <t>0.2%</t>
   </si>
   <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>0.0%</t>
-  </si>
-  <si>
-    <t>-8991</t>
-  </si>
-  <si>
-    <t>-3746</t>
-  </si>
-  <si>
-    <t>-478</t>
-  </si>
-  <si>
-    <t>-413</t>
-  </si>
-  <si>
-    <t>-322</t>
-  </si>
-  <si>
-    <t>-228</t>
-  </si>
-  <si>
-    <t>+170</t>
-  </si>
-  <si>
-    <t>+244</t>
-  </si>
-  <si>
-    <t>+318</t>
-  </si>
-  <si>
-    <t>+2281</t>
+    <t>-154</t>
+  </si>
+  <si>
+    <t>+239</t>
+  </si>
+  <si>
+    <t>+999</t>
   </si>
   <si>
     <t>+49900</t>
-  </si>
-  <si>
-    <t>+99900</t>
-  </si>
-  <si>
-    <t>Probability</t>
-  </si>
-  <si>
-    <t>52.8%</t>
-  </si>
-  <si>
-    <t>28.9%</t>
-  </si>
-  <si>
-    <t>5.8%</t>
-  </si>
-  <si>
-    <t>5.3%</t>
-  </si>
-  <si>
-    <t>5.1%</t>
-  </si>
-  <si>
-    <t>1.7%</t>
-  </si>
-  <si>
-    <t>-112</t>
-  </si>
-  <si>
-    <t>+246</t>
-  </si>
-  <si>
-    <t>+1624</t>
-  </si>
-  <si>
-    <t>+1787</t>
-  </si>
-  <si>
-    <t>+1861</t>
-  </si>
-  <si>
-    <t>+5782</t>
-  </si>
-  <si>
-    <t>59.4%</t>
-  </si>
-  <si>
-    <t>20.4%</t>
-  </si>
-  <si>
-    <t>16.6%</t>
-  </si>
-  <si>
-    <t>3.2%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
-  </si>
-  <si>
-    <t>-146</t>
-  </si>
-  <si>
-    <t>+390</t>
-  </si>
-  <si>
-    <t>+502</t>
-  </si>
-  <si>
-    <t>+3025</t>
-  </si>
-  <si>
-    <t>+33233</t>
   </si>
 </sst>
 </file>
@@ -611,7 +620,7 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="D2" t="s">
         <v>36</v>
@@ -622,10 +631,10 @@
         <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D3" t="s">
         <v>37</v>
@@ -636,10 +645,10 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="D4" t="s">
         <v>38</v>
@@ -653,7 +662,7 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="D5" t="s">
         <v>39</v>
@@ -667,7 +676,7 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="D6" t="s">
         <v>40</v>
@@ -678,10 +687,10 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="D7" t="s">
         <v>41</v>
@@ -695,7 +704,7 @@
         <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D8" t="s">
         <v>42</v>
@@ -706,10 +715,10 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="D9" t="s">
         <v>43</v>
@@ -720,10 +729,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="D10" t="s">
         <v>44</v>
@@ -734,10 +743,10 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C11" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
         <v>45</v>
@@ -748,10 +757,10 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
         <v>46</v>
@@ -762,10 +771,10 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C13" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D13" t="s">
         <v>47</v>
@@ -776,10 +785,10 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D14" t="s">
         <v>47</v>
@@ -790,7 +799,7 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
@@ -825,21 +834,21 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C2" t="s">
         <v>49</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B3" t="s">
         <v>18</v>
@@ -848,7 +857,7 @@
         <v>50</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -862,7 +871,7 @@
         <v>51</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -870,13 +879,13 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C5" t="s">
         <v>52</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>61</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -890,7 +899,7 @@
         <v>53</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>62</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -898,41 +907,41 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C7" t="s">
         <v>54</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>55</v>
       </c>
       <c r="D8" t="s">
-        <v>46</v>
+        <v>64</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B9" t="s">
         <v>20</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>56</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>65</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -940,10 +949,10 @@
         <v>12</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>34</v>
+        <v>57</v>
       </c>
       <c r="D10" t="s">
         <v>47</v>
@@ -954,7 +963,7 @@
         <v>15</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -965,10 +974,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C12" t="s">
         <v>35</v>
@@ -979,10 +988,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -993,10 +1002,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -1007,10 +1016,10 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
         <v>35</v>
@@ -1045,16 +1054,16 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C2" t="s">
-        <v>61</v>
+        <v>66</v>
       </c>
       <c r="D2" t="s">
-        <v>66</v>
+        <v>70</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -1062,77 +1071,77 @@
         <v>15</v>
       </c>
       <c r="B3" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="C3" t="s">
-        <v>62</v>
+        <v>67</v>
       </c>
       <c r="D3" t="s">
-        <v>67</v>
+        <v>71</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B4" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="C4" t="s">
-        <v>63</v>
+        <v>68</v>
       </c>
       <c r="D4" t="s">
-        <v>68</v>
+        <v>72</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="C5" t="s">
-        <v>64</v>
+        <v>56</v>
       </c>
       <c r="D5" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="B6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>65</v>
+        <v>69</v>
       </c>
       <c r="D6" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
         <v>20</v>
       </c>
       <c r="C7" t="s">
-        <v>34</v>
+        <v>69</v>
       </c>
       <c r="D7" t="s">
-        <v>47</v>
+        <v>73</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
         <v>35</v>
@@ -1143,7 +1152,7 @@
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B9" t="s">
         <v>18</v>
@@ -1157,10 +1166,10 @@
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C10" t="s">
         <v>35</v>
@@ -1174,7 +1183,7 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
         <v>35</v>
@@ -1185,10 +1194,10 @@
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>4</v>
+        <v>12</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C12" t="s">
         <v>35</v>
@@ -1199,10 +1208,10 @@
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
         <v>35</v>
@@ -1213,10 +1222,10 @@
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B14" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C14" t="s">
         <v>35</v>
@@ -1227,7 +1236,7 @@
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>

--- a/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
+++ b/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="70">
   <si>
     <t>Record</t>
   </si>
@@ -30,33 +30,33 @@
     <t>Team</t>
   </si>
   <si>
+    <t>Graesser's Golden Receivers</t>
+  </si>
+  <si>
+    <t>Yahya's Crew</t>
+  </si>
+  <si>
+    <t>Team Schottler</t>
+  </si>
+  <si>
     <t>MARVIN's Magnificent Team</t>
   </si>
   <si>
-    <t>Yahya's Crew</t>
-  </si>
-  <si>
-    <t>Graesser's Golden Receivers</t>
-  </si>
-  <si>
     <t>Dave's Dynamos</t>
   </si>
   <si>
+    <t>Hannah's Hail Mary</t>
+  </si>
+  <si>
     <t>Tracey Time</t>
   </si>
   <si>
-    <t>Team Schottler</t>
-  </si>
-  <si>
-    <t>Hannah's Hail Mary</t>
+    <t>Dale's Dangerous Team</t>
   </si>
   <si>
     <t>Sporty Jess</t>
   </si>
   <si>
-    <t>Dale's Dangerous Team</t>
-  </si>
-  <si>
     <t>Jeffrey's Team THAT NEVER WINS</t>
   </si>
   <si>
@@ -72,55 +72,49 @@
     <t>Laces Out Dan</t>
   </si>
   <si>
-    <t>5-1</t>
-  </si>
-  <si>
-    <t>4-2</t>
-  </si>
-  <si>
-    <t>3-3</t>
-  </si>
-  <si>
-    <t>2-4</t>
-  </si>
-  <si>
-    <t>0-6</t>
-  </si>
-  <si>
-    <t>1-5</t>
+    <t>5-2</t>
+  </si>
+  <si>
+    <t>4-3</t>
+  </si>
+  <si>
+    <t>3-4</t>
+  </si>
+  <si>
+    <t>1-6</t>
   </si>
   <si>
     <t>96.5%</t>
   </si>
   <si>
-    <t>95.2%</t>
-  </si>
-  <si>
-    <t>87.1%</t>
-  </si>
-  <si>
-    <t>86.6%</t>
-  </si>
-  <si>
-    <t>85.3%</t>
-  </si>
-  <si>
-    <t>74.3%</t>
-  </si>
-  <si>
-    <t>45.2%</t>
-  </si>
-  <si>
-    <t>12.4%</t>
-  </si>
-  <si>
-    <t>11.0%</t>
-  </si>
-  <si>
-    <t>5.0%</t>
-  </si>
-  <si>
-    <t>1.4%</t>
+    <t>87.6%</t>
+  </si>
+  <si>
+    <t>83.5%</t>
+  </si>
+  <si>
+    <t>81.7%</t>
+  </si>
+  <si>
+    <t>74.8%</t>
+  </si>
+  <si>
+    <t>74.4%</t>
+  </si>
+  <si>
+    <t>61.3%</t>
+  </si>
+  <si>
+    <t>25.7%</t>
+  </si>
+  <si>
+    <t>9.1%</t>
+  </si>
+  <si>
+    <t>3.4%</t>
+  </si>
+  <si>
+    <t>2.0%</t>
   </si>
   <si>
     <t>0.0%</t>
@@ -129,34 +123,34 @@
     <t>-2757</t>
   </si>
   <si>
-    <t>-1983</t>
-  </si>
-  <si>
-    <t>-675</t>
-  </si>
-  <si>
-    <t>-646</t>
-  </si>
-  <si>
-    <t>-580</t>
-  </si>
-  <si>
-    <t>-289</t>
-  </si>
-  <si>
-    <t>+121</t>
-  </si>
-  <si>
-    <t>+706</t>
-  </si>
-  <si>
-    <t>+809</t>
-  </si>
-  <si>
-    <t>+1900</t>
-  </si>
-  <si>
-    <t>+7043</t>
+    <t>-706</t>
+  </si>
+  <si>
+    <t>-506</t>
+  </si>
+  <si>
+    <t>-446</t>
+  </si>
+  <si>
+    <t>-297</t>
+  </si>
+  <si>
+    <t>-291</t>
+  </si>
+  <si>
+    <t>-158</t>
+  </si>
+  <si>
+    <t>+289</t>
+  </si>
+  <si>
+    <t>+999</t>
+  </si>
+  <si>
+    <t>+2841</t>
+  </si>
+  <si>
+    <t>+4900</t>
   </si>
   <si>
     <t>+99900</t>
@@ -165,79 +159,73 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>33.0%</t>
-  </si>
-  <si>
-    <t>28.6%</t>
-  </si>
-  <si>
-    <t>11.8%</t>
-  </si>
-  <si>
-    <t>11.2%</t>
-  </si>
-  <si>
-    <t>10.3%</t>
-  </si>
-  <si>
-    <t>4.2%</t>
-  </si>
-  <si>
-    <t>0.5%</t>
-  </si>
-  <si>
-    <t>0.3%</t>
+    <t>35.7%</t>
+  </si>
+  <si>
+    <t>20.9%</t>
+  </si>
+  <si>
+    <t>10.9%</t>
+  </si>
+  <si>
+    <t>10.8%</t>
+  </si>
+  <si>
+    <t>9.2%</t>
+  </si>
+  <si>
+    <t>7.8%</t>
+  </si>
+  <si>
+    <t>4.3%</t>
+  </si>
+  <si>
+    <t>0.4%</t>
+  </si>
+  <si>
+    <t>+180</t>
+  </si>
+  <si>
+    <t>+378</t>
+  </si>
+  <si>
+    <t>+817</t>
+  </si>
+  <si>
+    <t>+826</t>
+  </si>
+  <si>
+    <t>+987</t>
+  </si>
+  <si>
+    <t>+1182</t>
+  </si>
+  <si>
+    <t>+2226</t>
+  </si>
+  <si>
+    <t>+24900</t>
+  </si>
+  <si>
+    <t>80.9%</t>
+  </si>
+  <si>
+    <t>12.3%</t>
+  </si>
+  <si>
+    <t>6.7%</t>
   </si>
   <si>
     <t>0.1%</t>
   </si>
   <si>
-    <t>+203</t>
-  </si>
-  <si>
-    <t>+250</t>
-  </si>
-  <si>
-    <t>+747</t>
-  </si>
-  <si>
-    <t>+793</t>
-  </si>
-  <si>
-    <t>+871</t>
-  </si>
-  <si>
-    <t>+2281</t>
-  </si>
-  <si>
-    <t>+19900</t>
-  </si>
-  <si>
-    <t>+33233</t>
-  </si>
-  <si>
-    <t>60.7%</t>
-  </si>
-  <si>
-    <t>29.5%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>0.2%</t>
-  </si>
-  <si>
-    <t>-154</t>
-  </si>
-  <si>
-    <t>+239</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+49900</t>
+    <t>-424</t>
+  </si>
+  <si>
+    <t>+713</t>
+  </si>
+  <si>
+    <t>+1393</t>
   </si>
 </sst>
 </file>
@@ -620,10 +608,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -634,10 +622,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -648,10 +636,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -662,10 +650,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -676,10 +664,10 @@
         <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -687,13 +675,13 @@
         <v>9</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C7" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -701,13 +689,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -715,13 +703,13 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -732,10 +720,10 @@
         <v>20</v>
       </c>
       <c r="C10" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -743,13 +731,13 @@
         <v>13</v>
       </c>
       <c r="B11" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -757,13 +745,13 @@
         <v>14</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -771,13 +759,13 @@
         <v>15</v>
       </c>
       <c r="B13" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -785,13 +773,13 @@
         <v>16</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -799,13 +787,13 @@
         <v>17</v>
       </c>
       <c r="B15" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -826,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -834,86 +822,86 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="B2" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="D2" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="D3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D4" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="B5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D5" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D6" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="D7" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -921,13 +909,13 @@
         <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D8" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -935,41 +923,41 @@
         <v>11</v>
       </c>
       <c r="B9" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="D9" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>57</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="B11" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -977,13 +965,13 @@
         <v>16</v>
       </c>
       <c r="B12" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -991,13 +979,13 @@
         <v>14</v>
       </c>
       <c r="B13" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -1005,13 +993,13 @@
         <v>17</v>
       </c>
       <c r="B14" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1019,13 +1007,13 @@
         <v>13</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>
@@ -1046,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1057,41 +1045,41 @@
         <v>16</v>
       </c>
       <c r="B2" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="D2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="D3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B4" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="D4" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -1099,153 +1087,153 @@
         <v>13</v>
       </c>
       <c r="B5" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>56</v>
+        <v>66</v>
       </c>
       <c r="D5" t="s">
-        <v>65</v>
+        <v>45</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
         <v>20</v>
       </c>
       <c r="C6" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D6" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>14</v>
+        <v>4</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="D7" t="s">
-        <v>73</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D8" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B9" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D9" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D10" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="B11" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D11" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="B12" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D12" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B13" t="s">
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="B14" t="s">
         <v>18</v>
       </c>
       <c r="C14" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D14" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
     <row r="15" spans="1:4">
       <c r="A15" s="1" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="B15" t="s">
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="D15" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
     </row>
   </sheetData>

--- a/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
+++ b/data/odds/Loudoun Fantasy League (LFL) 2026 Betting Odds.xlsx
@@ -63,15 +63,15 @@
     <t>Yangblood Bravesheart</t>
   </si>
   <si>
+    <t>Laces Out Dan</t>
+  </si>
+  <si>
     <t>Bears, Jags, Foxes, Oh My!</t>
   </si>
   <si>
     <t>Ishan's Impressive Team</t>
   </si>
   <si>
-    <t>Laces Out Dan</t>
-  </si>
-  <si>
     <t>5-2</t>
   </si>
   <si>
@@ -84,73 +84,76 @@
     <t>1-6</t>
   </si>
   <si>
-    <t>96.5%</t>
-  </si>
-  <si>
-    <t>87.6%</t>
-  </si>
-  <si>
-    <t>83.5%</t>
-  </si>
-  <si>
-    <t>81.7%</t>
-  </si>
-  <si>
-    <t>74.8%</t>
-  </si>
-  <si>
-    <t>74.4%</t>
-  </si>
-  <si>
-    <t>61.3%</t>
-  </si>
-  <si>
-    <t>25.7%</t>
-  </si>
-  <si>
-    <t>9.1%</t>
-  </si>
-  <si>
-    <t>3.4%</t>
-  </si>
-  <si>
-    <t>2.0%</t>
+    <t>95.6%</t>
+  </si>
+  <si>
+    <t>88.3%</t>
+  </si>
+  <si>
+    <t>83.4%</t>
+  </si>
+  <si>
+    <t>80.7%</t>
+  </si>
+  <si>
+    <t>74.2%</t>
+  </si>
+  <si>
+    <t>73.3%</t>
+  </si>
+  <si>
+    <t>62.4%</t>
+  </si>
+  <si>
+    <t>26.0%</t>
+  </si>
+  <si>
+    <t>8.6%</t>
+  </si>
+  <si>
+    <t>5.0%</t>
+  </si>
+  <si>
+    <t>2.4%</t>
+  </si>
+  <si>
+    <t>0.1%</t>
   </si>
   <si>
     <t>0.0%</t>
   </si>
   <si>
-    <t>-2757</t>
-  </si>
-  <si>
-    <t>-706</t>
-  </si>
-  <si>
-    <t>-506</t>
-  </si>
-  <si>
-    <t>-446</t>
-  </si>
-  <si>
-    <t>-297</t>
-  </si>
-  <si>
-    <t>-291</t>
-  </si>
-  <si>
-    <t>-158</t>
-  </si>
-  <si>
-    <t>+289</t>
-  </si>
-  <si>
-    <t>+999</t>
-  </si>
-  <si>
-    <t>+2841</t>
-  </si>
-  <si>
-    <t>+4900</t>
+    <t>-2173</t>
+  </si>
+  <si>
+    <t>-755</t>
+  </si>
+  <si>
+    <t>-502</t>
+  </si>
+  <si>
+    <t>-418</t>
+  </si>
+  <si>
+    <t>-288</t>
+  </si>
+  <si>
+    <t>-275</t>
+  </si>
+  <si>
+    <t>-166</t>
+  </si>
+  <si>
+    <t>+285</t>
+  </si>
+  <si>
+    <t>+1063</t>
+  </si>
+  <si>
+    <t>+1900</t>
+  </si>
+  <si>
+    <t>+4067</t>
   </si>
   <si>
     <t>+99900</t>
@@ -159,73 +162,70 @@
     <t>Probability</t>
   </si>
   <si>
-    <t>35.7%</t>
-  </si>
-  <si>
-    <t>20.9%</t>
-  </si>
-  <si>
-    <t>10.9%</t>
-  </si>
-  <si>
-    <t>10.8%</t>
-  </si>
-  <si>
-    <t>9.2%</t>
-  </si>
-  <si>
-    <t>7.8%</t>
-  </si>
-  <si>
-    <t>4.3%</t>
+    <t>36.2%</t>
+  </si>
+  <si>
+    <t>20.6%</t>
+  </si>
+  <si>
+    <t>13.1%</t>
+  </si>
+  <si>
+    <t>11.2%</t>
+  </si>
+  <si>
+    <t>7.6%</t>
+  </si>
+  <si>
+    <t>6.2%</t>
+  </si>
+  <si>
+    <t>4.7%</t>
   </si>
   <si>
     <t>0.4%</t>
   </si>
   <si>
-    <t>+180</t>
-  </si>
-  <si>
-    <t>+378</t>
-  </si>
-  <si>
-    <t>+817</t>
-  </si>
-  <si>
-    <t>+826</t>
-  </si>
-  <si>
-    <t>+987</t>
-  </si>
-  <si>
-    <t>+1182</t>
-  </si>
-  <si>
-    <t>+2226</t>
+    <t>+176</t>
+  </si>
+  <si>
+    <t>+385</t>
+  </si>
+  <si>
+    <t>+663</t>
+  </si>
+  <si>
+    <t>+793</t>
+  </si>
+  <si>
+    <t>+1216</t>
+  </si>
+  <si>
+    <t>+1513</t>
+  </si>
+  <si>
+    <t>+2028</t>
   </si>
   <si>
     <t>+24900</t>
   </si>
   <si>
-    <t>80.9%</t>
-  </si>
-  <si>
-    <t>12.3%</t>
-  </si>
-  <si>
-    <t>6.7%</t>
-  </si>
-  <si>
-    <t>0.1%</t>
-  </si>
-  <si>
-    <t>-424</t>
-  </si>
-  <si>
-    <t>+713</t>
-  </si>
-  <si>
-    <t>+1393</t>
+    <t>81.5%</t>
+  </si>
+  <si>
+    <t>12.4%</t>
+  </si>
+  <si>
+    <t>6.1%</t>
+  </si>
+  <si>
+    <t>-441</t>
+  </si>
+  <si>
+    <t>+706</t>
+  </si>
+  <si>
+    <t>+1539</t>
   </si>
 </sst>
 </file>
@@ -611,7 +611,7 @@
         <v>22</v>
       </c>
       <c r="D2" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -625,7 +625,7 @@
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -639,7 +639,7 @@
         <v>24</v>
       </c>
       <c r="D4" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -653,7 +653,7 @@
         <v>25</v>
       </c>
       <c r="D5" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -667,7 +667,7 @@
         <v>26</v>
       </c>
       <c r="D6" t="s">
-        <v>38</v>
+        <v>39</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -681,7 +681,7 @@
         <v>27</v>
       </c>
       <c r="D7" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -695,7 +695,7 @@
         <v>28</v>
       </c>
       <c r="D8" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -709,7 +709,7 @@
         <v>29</v>
       </c>
       <c r="D9" t="s">
-        <v>41</v>
+        <v>42</v>
       </c>
     </row>
     <row r="10" spans="1:4">
@@ -723,7 +723,7 @@
         <v>30</v>
       </c>
       <c r="D10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -737,7 +737,7 @@
         <v>31</v>
       </c>
       <c r="D11" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
     </row>
     <row r="12" spans="1:4">
@@ -751,7 +751,7 @@
         <v>32</v>
       </c>
       <c r="D12" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -765,7 +765,7 @@
         <v>33</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4">
@@ -776,10 +776,10 @@
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -790,10 +790,10 @@
         <v>21</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -814,7 +814,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -828,10 +828,10 @@
         <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="D2" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="3" spans="1:4">
@@ -842,10 +842,10 @@
         <v>19</v>
       </c>
       <c r="C3" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D3" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
     </row>
     <row r="4" spans="1:4">
@@ -856,10 +856,10 @@
         <v>19</v>
       </c>
       <c r="C4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="D4" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="5" spans="1:4">
@@ -870,10 +870,10 @@
         <v>18</v>
       </c>
       <c r="C5" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D5" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="6" spans="1:4">
@@ -884,10 +884,10 @@
         <v>19</v>
       </c>
       <c r="C6" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="D6" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="7" spans="1:4">
@@ -898,10 +898,10 @@
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D7" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
     </row>
     <row r="8" spans="1:4">
@@ -912,10 +912,10 @@
         <v>18</v>
       </c>
       <c r="C8" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D8" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
     </row>
     <row r="9" spans="1:4">
@@ -926,24 +926,24 @@
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D9" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B10" t="s">
         <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4">
@@ -954,24 +954,24 @@
         <v>20</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B12" t="s">
         <v>21</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
@@ -982,24 +982,24 @@
         <v>19</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B14" t="s">
         <v>21</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1010,10 +1010,10 @@
         <v>20</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
@@ -1034,7 +1034,7 @@
         <v>0</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D1" s="1" t="s">
         <v>2</v>
@@ -1042,13 +1042,13 @@
     </row>
     <row r="2" spans="1:4">
       <c r="A2" s="1" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="B2" t="s">
         <v>21</v>
       </c>
       <c r="C2" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D2" t="s">
         <v>67</v>
@@ -1056,13 +1056,13 @@
     </row>
     <row r="3" spans="1:4">
       <c r="A3" s="1" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="B3" t="s">
         <v>21</v>
       </c>
       <c r="C3" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D3" t="s">
         <v>68</v>
@@ -1070,13 +1070,13 @@
     </row>
     <row r="4" spans="1:4">
       <c r="A4" s="1" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="B4" t="s">
         <v>21</v>
       </c>
       <c r="C4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
         <v>69</v>
@@ -1084,142 +1084,142 @@
     </row>
     <row r="5" spans="1:4">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" t="s">
         <v>20</v>
       </c>
       <c r="C5" t="s">
-        <v>66</v>
+        <v>34</v>
       </c>
       <c r="D5" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="6" spans="1:4">
       <c r="A6" s="1" t="s">
-        <v>12</v>
+        <v>4</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="C6" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D6" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" spans="1:4">
       <c r="A7" s="1" t="s">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="B7" t="s">
         <v>18</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D7" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:4">
       <c r="A8" s="1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="C8" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D8" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="9" spans="1:4">
       <c r="A9" s="1" t="s">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="B9" t="s">
         <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D9" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10" spans="1:4">
       <c r="A10" s="1" t="s">
-        <v>6</v>
+        <v>11</v>
       </c>
       <c r="B10" t="s">
         <v>19</v>
       </c>
       <c r="C10" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="11" spans="1:4">
       <c r="A11" s="1" t="s">
-        <v>11</v>
+        <v>5</v>
       </c>
       <c r="B11" t="s">
         <v>19</v>
       </c>
       <c r="C11" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D11" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="12" spans="1:4">
       <c r="A12" s="1" t="s">
-        <v>5</v>
+        <v>14</v>
       </c>
       <c r="B12" t="s">
         <v>19</v>
       </c>
       <c r="C12" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D12" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="13" spans="1:4">
       <c r="A13" s="1" t="s">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C13" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D13" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="14" spans="1:4">
       <c r="A14" s="1" t="s">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="B14" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="C14" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D14" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:4">
@@ -1230,10 +1230,10 @@
         <v>18</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
